--- a/data/trans_bre/P29A_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P29A_R-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-35,94; -28,85</t>
+          <t>-35,65; -28,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-38,37; -30,95</t>
+          <t>-38,47; -30,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-36,82; -28,29</t>
+          <t>-36,75; -28,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-43,16; -34,38</t>
+          <t>-43,23; -34,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-77,97; -69,27</t>
+          <t>-78,25; -69,63</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-74,85; -65,88</t>
+          <t>-74,96; -65,62</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-76,73; -65,36</t>
+          <t>-76,96; -66,33</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-84,43; -76,78</t>
+          <t>-84,62; -76,51</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-32,21; -25,13</t>
+          <t>-32,29; -25,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-31,57; -24,86</t>
+          <t>-31,2; -24,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-26,98; -20,63</t>
+          <t>-27,44; -20,9</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-22,37; 14,65</t>
+          <t>-21,93; 9,6</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-52,18; -43,05</t>
+          <t>-52,4; -43,47</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-53,87; -44,38</t>
+          <t>-53,5; -44,28</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-45,04; -36,05</t>
+          <t>-45,52; -36,45</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-47,39; 41,7</t>
+          <t>-46,65; 27,72</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-28,06; -16,0</t>
+          <t>-28,42; -15,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-26,62; -12,66</t>
+          <t>-26,73; -12,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-23,99; -11,87</t>
+          <t>-24,18; -11,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-21,75; -11,12</t>
+          <t>-21,49; -10,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-44,56; -27,18</t>
+          <t>-45,44; -27,74</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-38,83; -20,09</t>
+          <t>-39,29; -20,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-33,97; -18,21</t>
+          <t>-34,36; -18,38</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-38,35; -21,85</t>
+          <t>-37,75; -21,3</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-32,71; -28,28</t>
+          <t>-32,58; -27,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-32,74; -28,09</t>
+          <t>-32,74; -28,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-28,6; -23,83</t>
+          <t>-28,6; -23,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-24,95; -3,69</t>
+          <t>-25,08; 0,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-58,35; -52,46</t>
+          <t>-58,29; -52,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-57,2; -51,12</t>
+          <t>-57,45; -51,02</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-49,17; -42,5</t>
+          <t>-49,25; -42,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-50,89; -9,19</t>
+          <t>-51,11; 3,08</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P29A_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P29A_R-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-38,62</t>
+          <t>-35,71</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-81,16%</t>
+          <t>-79,61%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-35,65; -28,58</t>
+          <t>-35,42; -28,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-38,47; -30,54</t>
+          <t>-38,38; -30,84</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-36,75; -28,25</t>
+          <t>-36,52; -28,41</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-43,23; -34,12</t>
+          <t>-40,06; -31,45</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-78,25; -69,63</t>
+          <t>-78,11; -69,18</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-74,96; -65,62</t>
+          <t>-75,1; -65,95</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-76,96; -66,33</t>
+          <t>-76,72; -66,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-84,62; -76,51</t>
+          <t>-83,46; -75,18</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-11,36</t>
+          <t>-21,22</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-26,33%</t>
+          <t>-45,09%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-32,29; -25,38</t>
+          <t>-32,28; -25,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-31,2; -24,74</t>
+          <t>-31,46; -24,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-27,44; -20,9</t>
+          <t>-26,81; -20,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-21,93; 9,6</t>
+          <t>-24,4; -18,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-52,4; -43,47</t>
+          <t>-52,1; -43,45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-53,5; -44,28</t>
+          <t>-53,56; -44,47</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-45,52; -36,45</t>
+          <t>-44,4; -36,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-46,65; 27,72</t>
+          <t>-49,58; -40,41</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-15,82</t>
+          <t>-14,85</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-29,72%</t>
+          <t>-28,71%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-28,42; -15,68</t>
+          <t>-27,83; -15,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-26,73; -12,68</t>
+          <t>-26,86; -12,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-24,18; -11,88</t>
+          <t>-23,84; -11,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-21,49; -10,77</t>
+          <t>-20,0; -9,56</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-45,44; -27,74</t>
+          <t>-44,6; -26,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-39,29; -20,32</t>
+          <t>-39,78; -20,83</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-34,36; -18,38</t>
+          <t>-34,0; -18,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-37,75; -21,3</t>
+          <t>-36,62; -19,54</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-17,6</t>
+          <t>-23,31</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-38,52%</t>
+          <t>-48,92%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-32,58; -27,95</t>
+          <t>-32,84; -28,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-32,74; -28,03</t>
+          <t>-32,61; -27,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-28,6; -23,89</t>
+          <t>-28,66; -23,88</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-25,08; 0,64</t>
+          <t>-25,53; -21,17</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-58,29; -52,1</t>
+          <t>-58,51; -52,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-57,45; -51,02</t>
+          <t>-56,92; -51,02</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-49,25; -42,93</t>
+          <t>-49,29; -42,97</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-51,11; 3,08</t>
+          <t>-52,13; -45,69</t>
         </is>
       </c>
     </row>
